--- a/stories/arbres/ATOM-TMP.JOU.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Oscar est dans le jardin avec maman. C'est le jour. Le soleil brille. Maman dit : le jour, le soleil. Soleil jour. Oscar sent la chaleur sur ses mains. Les oiseaux chantent. L'herbe chatouille. Plus tard, le soir arrive. Oscar est dans sa chambre. La fenêtre est ouverte un peu. Il voit la lune. Il voit les étoiles. Maman dit : la nuit, la lune et les étoiles. Lune nuit. Oscar met son pyjama. Le pyjama est doux. Maman dit : on se couche. Dodo la nuit. Oscar se couche. Le corps a besoin de dormir. Même leçon, deux moments. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
+          <t>Oscar est dans le jardin avec maman. C'est le jour. Le soleil brille. Le jour, le soleil. Soleil jour. Oscar sent la chaleur sur ses mains. Les oiseaux chantent. L'herbe chatouille. Plus tard, le soir arrive. Oscar est dans sa chambre. La fenêtre est ouverte un peu. Il voit la lune. Il voit les étoiles. La nuit, la lune et les étoiles. Lune nuit. Oscar met son pyjama. Le pyjama est doux. On se couche. Dodo la nuit. Oscar se couche. Le corps a besoin de dormir. Même leçon, deux moments. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Oscar est dans le jardin avec maman. C'est le jour. Le soleil brille.
+maman|Le jour, le soleil. Soleil jour.
+narrateur|Oscar sent la chaleur sur ses mains. Les oiseaux chantent. L'herbe chatouille. Plus tard, le soir arrive. Oscar est dans sa chambre. La fenêtre est ouverte un peu. Il voit la lune. Il voit les étoiles.
+maman|La nuit, la lune et les étoiles. Lune nuit.
+narrateur|Oscar met son pyjama. Le pyjama est doux.
+maman|On se couche. Dodo la nuit.
+narrateur|Oscar se couche. Le corps a besoin de dormir. Même leçon, deux moments. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le jour on voit le soleil. La nuit, que voit-on ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Oscar a vu le soleil le jour. Puis la lune la nuit. Dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Oscar ferme les yeux. La lune est là.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Oscar se couche. Le corps a besoin de dormir. Même leçon, deux moments. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Le jour on voit le soleil. La nuit, que voit-on ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Oscar a vu le soleil le jour. Puis la lune la nuit. Dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Oscar ferme les yeux. La lune est là.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.JOU.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oscar voit le soleil, puis la lune</t>
+          <t>Le coquillage de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut un coquillage. Le soleil chauffe le sable. Une vague remplit la coquille. Le soir, la lune est dans la vitre, le coquillage sur la table.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Oscar est dans le jardin avec maman. C'est le jour. Le soleil brille. Le jour, le soleil. Soleil jour. Oscar sent la chaleur sur ses mains. Les oiseaux chantent. L'herbe chatouille. Plus tard, le soir arrive. Oscar est dans sa chambre. La fenêtre est ouverte un peu. Il voit la lune. Il voit les étoiles. La nuit, la lune et les étoiles. Lune nuit. Oscar met son pyjama. Le pyjama est doux. On se couche. Dodo la nuit. Oscar se couche. Le corps a besoin de dormir. Même leçon, deux moments. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
+          <t>Le sel colle déjà aux genoux de Nina. Le sable est tiède et rêche. Une vague vient, puis recule. Ça sent l'iode et le chaud. Tu as senti l'eau, Nina ? Elle est froide aux pieds. Oui. Plus loin, elle brille. Je veux un coquillage. On en cherche un, près de l'écume. En ce moment, Nina marche au bord. Le soleil tape ses épaules, fort. Son ombre est toute courte, devant elle. Le jour est long, ici. Le soleil est sur la mer. Nina ramasse une coquille beige. Elle est pleine de sable mouillé. Il y a du sable. On la rince ? Oui. Une vague plus vive arrive. L'eau prend la coquille, un instant. Oh. Nina la reprend, ruisselante. Elle la plonge dans une flaque claire. Le sable part, le rose apparaît. Elle est rose dedans. Merci, Nina. Tu l'as rincée. Ils restent encore un peu. Les épaules de Nina piquent, chaudes. Un bateau passe, tout petit. Il va loin. Comme nous, tout à l'heure. Plus tard, le sable refroidit. Le ciel se teinte de mauve. On rentre. Dans la voiture, la coquille tient dans un gant. La mer recule derrière les dunes. La vitre s'assombrit. Une lune ronde glisse sur le verre. Elle nous suit. La nuit est là. La lune est dans la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oscar est dans le jardin avec maman. C'est le jour. Le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; brille. Maman dit : le jour, le soleil. Soleil jour. Oscar sent la chaleur sur ses mains. Les oiseaux chantent. L'herbe chatouille. Plus tard, le soir arrive. Oscar est dans sa chambre. La fenêtre est ouverte un peu. Il voit la lune. Il voit les étoiles. Maman dit : la nuit, la lune et les étoiles. Lune nuit. Oscar met son pyjama. Le pyjama est doux. Maman dit : on se couche. Dodo la nuit. Oscar se couche. Le corps a besoin de dormir. Même leçon, deux moments. Le jour le soleil. La nuit la lune. Dodo la nuit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sel colle déjà aux genoux de Nina. Le sable est tiède et rêche. Une vague vient, puis recule. Ça sent l'iode et le chaud. Tu as senti l'eau, Nina ? Elle est froide aux pieds. Oui. Plus loin, elle brille. Je veux un coquillage. On en cherche un, près de l'écume. En ce moment, Nina marche au bord. Le soleil tape ses épaules, fort. Son ombre est toute courte, devant elle. Le jour est long, ici. Le soleil est sur la mer. Nina ramasse une coquille beige. Elle est pleine de sable mouillé. Il y a du sable. On la rince ? Oui. Une vague plus vive arrive. L'eau prend la coquille, un instant. Oh. Nina la reprend, ruisselante. Elle la plonge dans une flaque claire. Le sable part, le rose apparaît. Elle est rose dedans. Merci, Nina. Tu l'as rincée. Ils restent encore un peu. Les épaules de Nina piquent, chaudes. Un bateau passe, tout petit. Il va loin. Comme nous, tout à l'heure. Plus tard, le sable refroidit. Le ciel se teinte de mauve. On rentre. Dans la voiture, la coquille tient dans un gant. La mer recule derrière les dunes. La vitre s'assombrit. Une lune ronde glisse sur le verre. Elle nous suit. La nuit est là. La lune est dans la vitre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,16 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Oscar est dans le jardin avec maman. C'est le jour. Le soleil brille.
-maman|Le jour, le soleil. Soleil jour.
-narrateur|Oscar sent la chaleur sur ses mains. Les oiseaux chantent. L'herbe chatouille. Plus tard, le soir arrive. Oscar est dans sa chambre. La fenêtre est ouverte un peu. Il voit la lune. Il voit les étoiles.
-maman|La nuit, la lune et les étoiles. Lune nuit.
-narrateur|Oscar met son pyjama. Le pyjama est doux.
-maman|On se couche. Dodo la nuit.
-narrateur|Oscar se couche. Le corps a besoin de dormir. Même leçon, deux moments. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le sel colle déjà aux genoux de Nina.
+narrateur|Le sable est tiède et rêche.
+narrateur|Une vague vient, puis recule.
+narrateur|Ça sent l'iode et le chaud.
+maman|Tu as senti l'eau, Nina ?
+enfant-f|Elle est froide aux pieds.
+maman|Oui.
+maman|Plus loin, elle brille.
+enfant-f|Je veux un coquillage.
+maman|On en cherche un, près de l'écume.
+narrateur|En ce moment, Nina marche au bord.
+narrateur|Le soleil tape ses épaules, fort.
+narrateur|Son ombre est toute courte, devant elle.
+maman|Le jour est long, ici.
+maman|Le soleil est sur la mer.
+narrateur|Nina ramasse une coquille beige.
+narrateur|Elle est pleine de sable mouillé.
+enfant-f|Il y a du sable.
+maman|On la rince ?
+enfant-f|Oui.
+narrateur|Une vague plus vive arrive.
+narrateur|L'eau prend la coquille, un instant.
+enfant-f|Oh.
+narrateur|Nina la reprend, ruisselante.
+narrateur|Elle la plonge dans une flaque claire.
+narrateur|Le sable part, le rose apparaît.
+enfant-f|Elle est rose dedans.
+maman|Merci, Nina.
+maman|Tu l'as rincée.
+narrateur|Ils restent encore un peu.
+narrateur|Les épaules de Nina piquent, chaudes.
+narrateur|Un bateau passe, tout petit.
+enfant-f|Il va loin.
+maman|Comme nous, tout à l'heure.
+narrateur|Plus tard, le sable refroidit.
+narrateur|Le ciel se teinte de mauve.
+maman|On rentre.
+narrateur|Dans la voiture, la coquille tient dans un gant.
+narrateur|La mer recule derrière les dunes.
+narrateur|La vitre s'assombrit.
+narrateur|Une lune ronde glisse sur le verre.
+enfant-f|Elle nous suit.
+maman|La nuit est là.
+maman|La lune est dans la vitre.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>vagues</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,12 +1399,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le jour on voit le soleil. La nuit, que voit-on ?</t>
+          <t>Nina est rentrée. La nuit, que voit-elle à la vitre ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le jour on voit le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt;. La nuit, que voit-on ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina est rentrée. La nuit, que voit-elle à la vitre ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1361,12 +1414,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la lune</t>
+          <t>lune</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la lune | lune | étoiles | la nuit | soleil</t>
+          <t>lune | la lune | la lune dans la vitre | la lune à la fenêtre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1434,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le jour, le soleil. La nuit, la lune. Que voit-on la nuit ?</t>
+          <t>Le jour, le soleil. La nuit, à la vitre, que voit-on ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1423,14 +1476,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le jour on voit le soleil. La nuit, que voit-on ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina est rentrée.
+narrateur|La nuit, que voit-elle à la vitre ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Oscar a vu le soleil le jour. Puis la lune la nuit. Dodo la nuit.</t>
+          <t>Nina a marché au soleil, le sable chaud. Maintenant la lune est sur la vitre. Le jour, c'était le soleil sur la mer. La nuit, c'est la lune. Elle est ronde, comme le coquillage. Un peu, oui. La coquille pose une tache d'eau sur le gant. Elle est encore mouillée. On la met près de la fenêtre ? Oui. La maison sent le sel, encore. Le pyjama, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oscar a vu le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; le jour. Puis la lune la nuit. Dodo la nuit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a marché au soleil, le sable chaud. Maintenant la lune est sur la vitre. Le jour, c'était le soleil sur la mer. La nuit, c'est la lune. Elle est ronde, comme le coquillage. Un peu, oui. La coquille pose une tache d'eau sur le gant. Elle est encore mouillée. On la met près de la fenêtre ? Oui. La maison sent le sel, encore. Le pyjama, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1602,7 +1655,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1731,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Oscar a vu le soleil le jour. Puis la lune la nuit. Dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a marché au soleil, le sable chaud.
+narrateur|Maintenant la lune est sur la vitre.
+maman|Le jour, c'était le soleil sur la mer.
+maman|La nuit, c'est la lune.
+enfant-f|Elle est ronde, comme le coquillage.
+maman|Un peu, oui.
+narrateur|La coquille pose une tache d'eau sur le gant.
+enfant-f|Elle est encore mouillée.
+maman|On la met près de la fenêtre ?
+enfant-f|Oui.
+narrateur|La maison sent le sel, encore.
+maman|Le pyjama, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Oscar ferme les yeux. La lune est là.</t>
+          <t>Nina enfile le pyjama, un peu rêche de sel. Elle pose le coquillage sur la table. La lune le touche, pâle. La nuit, on se couche. Tu fermes les yeux ? Je regarde encore. Dehors, la mer n'est plus qu'un souffle. Dedans, le verre de la fenêtre est froid. Elle est toujours là. Oui. La lune reste. Maman baisse la lumière. Nina respire l'iode sur sa peau.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oscar ferme les yeux. La &lt;emphasis level="moderate"&gt;lune&lt;/emphasis&gt; est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina enfile le pyjama, un peu rêche de sel. Elle pose le coquillage sur la table. La lune le touche, pâle. La nuit, on se couche. Tu fermes les yeux ? Je regarde encore. Dehors, la mer n'est plus qu'un souffle. Dedans, le verre de la fenêtre est froid. Elle est toujours là. Oui. La lune reste. Maman baisse la lumière. Nina respire l'iode sur sa peau.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1774,7 +1837,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1846,10 +1909,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Oscar ferme les yeux. La lune est là.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina enfile le pyjama, un peu rêche de sel.
+narrateur|Elle pose le coquillage sur la table.
+narrateur|La lune le touche, pâle.
+maman|La nuit, on se couche.
+maman|Tu fermes les yeux ?
+enfant-f|Je regarde encore.
+narrateur|Dehors, la mer n'est plus qu'un souffle.
+narrateur|Dedans, le verre de la fenêtre est froid.
+enfant-f|Elle est toujours là.
+maman|Oui.
+maman|La lune reste.
+narrateur|Maman baisse la lumière.
+narrateur|Nina respire l'iode sur sa peau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1874,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le coquillage sèche tout doux. Le rose dedans devient mat. Il a gardé la mer. Un peu, oui. La lune reste collée à la vitre. Nina ferme les yeux, le sel aux genoux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le coquillage sèche tout doux. Le rose dedans devient mat. Il a gardé la mer. Un peu, oui. La lune reste collée à la vitre. Nina ferme les yeux, le sel aux genoux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1942,7 +2016,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2014,10 +2088,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le coquillage sèche tout doux.
+narrateur|Le rose dedans devient mat.
+enfant-f|Il a gardé la mer.
+maman|Un peu, oui.
+narrateur|La lune reste collée à la vitre.
+narrateur|Nina ferme les yeux, le sel aux genoux.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2036,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin le jour puis chambre la nuit</t>
+          <t>mer le jour, voiture puis chambre la nuit</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oscar, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
